--- a/Roster_(KEA).xlsx
+++ b/Roster_(KEA).xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mbonner/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mbonner/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{975FD435-3D85-B145-B972-4E1649AFC0FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF9C1650-672C-2646-A64F-52B6A45F35C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1720" yWindow="660" windowWidth="14140" windowHeight="20560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
